--- a/financial_models/opportunities/0700.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0700.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22F2969-A1EB-402E-930A-2B6B05B5EDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DEAA7E-3EA8-41D1-AD38-239BD1B662C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,7 +3785,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="50">
-        <v>0.93200000000000005</v>
+        <v>1.07197944</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="C20" s="259">
         <f>C123</f>
-        <v>136.31504787998466</v>
+        <v>156.60505097964941</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>342</v>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.22857688359124895</v>
+        <v>-0.19189388513342065</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
-        <v>4.6879187579356316E-2</v>
+        <v>5.392009146885552E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C73" s="255">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>266.43004940934173</v>
+        <v>306.44585318132886</v>
       </c>
       <c r="D73" s="1" t="str">
         <f>Market_currency</f>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C82" s="255">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
-        <v>22.986799272775702</v>
+        <v>26.439244862470499</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="C87" s="255">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>-2.6033601603213734</v>
+        <v>-2.9943654149995882</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="C95" s="255">
         <f>Valuation_Model!C12</f>
-        <v>240.83988997624465</v>
+        <v>277.01224290385875</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="E102" s="265" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>321.4 HKD</v>
+        <v>369.68 HKD</v>
       </c>
       <c r="F102" s="266">
         <f>Valuation_Model!F74</f>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="E103" s="252" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>258.69 HKD</v>
+        <v>297.55 HKD</v>
       </c>
       <c r="F103" s="253">
         <f>Valuation_Model!F75</f>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="E104" s="252" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>240.84 HKD</v>
+        <v>277.01 HKD</v>
       </c>
       <c r="F104" s="253">
         <f>Valuation_Model!F76</f>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="E105" s="252" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>202.89 HKD</v>
+        <v>233.36 HKD</v>
       </c>
       <c r="F105" s="253">
         <f>Valuation_Model!F77</f>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="E106" s="252" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>68.59 HKD</v>
+        <v>78.9 HKD</v>
       </c>
       <c r="F106" s="253">
         <f>Valuation_Model!F78</f>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C108" s="248">
         <f>Scenarios!C60</f>
-        <v>233.44120273661346</v>
+        <v>268.50232809283415</v>
       </c>
       <c r="D108" s="243" t="str">
         <f>Market_currency</f>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C122" s="247">
         <f>Scenarios!C82</f>
-        <v>135.09328862072539</v>
+        <v>155.38329172039013</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C123" s="246">
         <f>Scenarios!C83</f>
-        <v>136.31504787998466</v>
+        <v>156.60505097964941</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="C124" s="158">
         <f>Scenarios!F83</f>
-        <v>-0.41606260470742218</v>
+        <v>-0.41674602193578181</v>
       </c>
     </row>
   </sheetData>
@@ -7782,11 +7782,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-23.640907569734086</v>
+        <v>-27.191595340874791</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-62.610983201235264</v>
+        <v>-72.014685311061783</v>
       </c>
       <c r="F47" s="291"/>
     </row>
@@ -8189,11 +8189,11 @@
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-210991.75200000001</v>
+        <v>-242681.13750384</v>
       </c>
       <c r="D86" s="255">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-22.986799272775702</v>
+        <v>-26.439244862470499</v>
       </c>
       <c r="E86" s="277" t="str">
         <f>Market_currency</f>
@@ -8206,11 +8206,11 @@
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-23895.781000000003</v>
+        <v>-27484.74885702</v>
       </c>
       <c r="D87" s="255">
         <f>C87*$H$1/Common_Shares</f>
-        <v>-2.6033601603213739</v>
+        <v>-2.9943654149995882</v>
       </c>
       <c r="E87" s="277" t="str">
         <f>Market_currency</f>
@@ -8240,11 +8240,11 @@
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
-        <v>-234887.533</v>
+        <v>-270165.88636086002</v>
       </c>
       <c r="D89" s="279">
         <f>SUM(D86:D88)</f>
-        <v>-25.590159433097075</v>
+        <v>-29.433610277470088</v>
       </c>
       <c r="E89" s="277" t="str">
         <f>Market_currency</f>
@@ -12893,14 +12893,14 @@
       </c>
       <c r="C119" s="182">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>23.978704446840759</v>
+        <v>27.580126786319596</v>
       </c>
       <c r="D119" s="27"/>
       <c r="E119" s="309"/>
       <c r="F119" s="27"/>
       <c r="G119" s="182">
         <f t="shared" ref="G119:Q119" si="48">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>58.199696951087304</v>
+        <v>66.940856808794294</v>
       </c>
       <c r="H119" s="182" t="str">
         <f t="shared" si="48"/>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="I119" s="182">
         <f t="shared" si="48"/>
-        <v>51.171477664096578</v>
+        <v>58.857051470311973</v>
       </c>
       <c r="J119" s="182" t="str">
         <f t="shared" si="48"/>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M119" s="182">
         <f t="shared" si="48"/>
-        <v>34.833246805550438</v>
+        <v>40.064940347634916</v>
       </c>
       <c r="N119" s="182" t="str">
         <f t="shared" si="48"/>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="O119" s="182">
         <f t="shared" si="48"/>
-        <v>37.390990984436144</v>
+        <v>43.006838601438744</v>
       </c>
       <c r="P119" s="182" t="str">
         <f t="shared" si="48"/>
@@ -12950,14 +12950,14 @@
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.6879187579356316E-2</v>
+        <v>5.392009146885552E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="309"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
-        <v>0.11378239873135348</v>
+        <v>0.13087166531533587</v>
       </c>
       <c r="H120" s="79" t="str">
         <f t="shared" ref="H120" si="50">IF(H$4="","",H119/Market_Price)</f>
@@ -12965,7 +12965,7 @@
       </c>
       <c r="I120" s="79">
         <f t="shared" ref="I120" si="51">IF(I$4="","",I119/Market_Price)</f>
-        <v>0.10004198956812625</v>
+        <v>0.11506754930657277</v>
       </c>
       <c r="J120" s="79" t="str">
         <f t="shared" ref="J120" si="52">IF(J$4="","",J119/Market_Price)</f>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="M120" s="79">
         <f t="shared" ref="M120" si="55">IF(M$4="","",M119/Market_Price)</f>
-        <v>6.8100189258163121E-2</v>
+        <v>7.8328329125385954E-2</v>
       </c>
       <c r="N120" s="79" t="str">
         <f t="shared" ref="N120" si="56">IF(N$4="","",N119/Market_Price)</f>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="O120" s="79">
         <f t="shared" ref="O120" si="57">IF(O$4="","",O119/Market_Price)</f>
-        <v>7.3100666636238792E-2</v>
+        <v>8.4079840863027847E-2</v>
       </c>
       <c r="P120" s="79" t="str">
         <f t="shared" ref="P120" si="58">IF(P$4="","",P119/Market_Price)</f>
@@ -13856,7 +13856,7 @@
       </c>
       <c r="C11" s="238">
         <f>Exchange_Rate</f>
-        <v>0.93200000000000005</v>
+        <v>1.07197944</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>240.83988997624465</v>
+        <v>277.01224290385875</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13923,7 +13923,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>233.50967482415533</v>
+        <v>268.58108417658809</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14859,23 +14859,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>240.83988997624465</v>
+        <v>277.01224290385875</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>240.83988997624465</v>
+        <v>277.01224290385875</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>240.83988997624465</v>
+        <v>277.01224290385875</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>240.83988997624465</v>
+        <v>277.01224290385875</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>240.83988997624465</v>
+        <v>277.01224290385875</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14886,23 +14886,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>133.96012879676144</v>
+        <v>154.07993975309034</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>219.7967463353809</v>
+        <v>252.80857623436015</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>240.83988997624454</v>
+        <v>277.01224290385858</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>249.71411835068747</v>
+        <v>287.21931410908121</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>263.55171055272859</v>
+        <v>303.13520932334347</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -14913,23 +14913,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>95.715053017730568</v>
+        <v>110.09073919905271</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>202.88612973372398</v>
+        <v>233.35811130442571</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>240.83988997624454</v>
+        <v>277.01224290385858</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>258.69376560678808</v>
+        <v>297.5476373247381</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>288.92604679624577</v>
+        <v>332.32058137988554</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -14940,23 +14940,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>68.594073544706433</v>
+        <v>78.896391143533492</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>185.91480866473145</v>
+        <v>213.83782454949139</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>240.83988997624454</v>
+        <v>277.01224290385858</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>269.31991212046472</v>
+        <v>309.76975169071352</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>321.40305815079006</v>
+        <v>369.6753973076946</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -14967,23 +14967,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>50.719958808595386</v>
+        <v>58.337717854572041</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>171.87695344573356</v>
+        <v>197.69158830865186</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>240.83988997624454</v>
+        <v>277.01224290385858</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>279.66336517396718</v>
+        <v>321.66671414989787</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>355.77073170968993</v>
+        <v>409.2048387838451</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -14994,23 +14994,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>39.075992824387292</v>
+        <v>44.944915134475011</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>161.2407444442596</v>
+        <v>185.45790014435678</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>240.83988997624448</v>
+        <v>277.01224290385852</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>288.85234543298287</v>
+        <v>332.23581062224844</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>389.10634208528541</v>
+        <v>447.5472088938119</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15020,23 +15020,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>31.505262607128078</v>
+        <v>36.237117775367054</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>153.56726195867196</v>
+        <v>176.63191789355201</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>240.83988997624454</v>
+        <v>277.01224290385858</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>296.59441608266923</v>
+        <v>341.14068246719609</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>419.89580590571865</v>
+        <v>482.96102025017268</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>321.40305815079006</v>
+        <v>369.6753973076946</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>258.69376560678808</v>
+        <v>297.5476373247381</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>240.83988997624454</v>
+        <v>277.01224290385858</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>202.88612973372398</v>
+        <v>233.35811130442571</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>68.594073544706433</v>
+        <v>78.896391143533492</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I6" s="272">
         <f t="shared" si="0"/>
-        <v>234.02120273661347</v>
+        <v>269.08232809283413</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
-        <v>240.83988997624465</v>
+        <v>277.01224290385875</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
-        <v>240.83988997624454</v>
+        <v>277.01224290385858</v>
       </c>
       <c r="D27" s="165" t="str">
         <f>Market_currency</f>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
-        <v>202.88612973372398</v>
+        <v>233.35811130442571</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15681,7 +15681,7 @@
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
-        <v>258.69376560678808</v>
+        <v>297.5476373247381</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>237.71260683537631</v>
+        <v>273.41526518919193</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
-        <v>68.594073544706433</v>
+        <v>78.896391143533492</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
-        <v>321.40305815079006</v>
+        <v>369.6753973076946</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>233.44120273661346</v>
+        <v>268.50232809283415</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -15927,7 +15927,7 @@
       </c>
       <c r="C66" s="165">
         <f>Valuation_Model!C18</f>
-        <v>233.50967482415533</v>
+        <v>268.58108417658809</v>
       </c>
       <c r="D66" s="165" t="str">
         <f>Market_currency</f>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>135.09328862072539</v>
+        <v>155.38329172039013</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16069,7 +16069,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>136.31504787998466</v>
+        <v>156.60505097964941</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16080,7 +16080,7 @@
       </c>
       <c r="F83" s="270">
         <f>(C83/C60-1)</f>
-        <v>-0.41606260470742218</v>
+        <v>-0.41674602193578181</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-0.22857688359124895</v>
+        <v>-0.19189388513342065</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
